--- a/Restaurant Management/results/BHB_Kingsville_sorted_Kingsville_Payroll.xlsx
+++ b/Restaurant Management/results/BHB_Kingsville_sorted_Kingsville_Payroll.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,7 +43,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -52,12 +52,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
       <left style="thick">
         <color rgb="00000000"/>
       </left>
@@ -159,18 +153,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -179,20 +173,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -560,211 +551,215 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Employee</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Job Title</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Regular Hours</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Overtime Hours</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Declared Tips</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Non-Cash Tips</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Total Tips</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Adam Oviedo</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Adrian Jesus Gonzalez</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
-        <v>29.52</v>
+      <c r="C2" s="5" t="n">
+        <v>37.11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Adrian Jesus Gonzalez</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>35.07</v>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Alexa Rae Garcia</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Alexa Rae Garcia</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="D4" s="9" t="inlineStr"/>
-      <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="8" t="n">
-        <v>122.24</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>122.24</v>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Alexandra Perez</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>124.96</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>124.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Alexa Rae Garcia</t>
+          <t>Alyssa Rodriguez</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>BAR</t>
+          <t>SERVER</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr"/>
+        <v>32.63</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>7.56</v>
+      </c>
       <c r="E5" s="9" t="inlineStr"/>
       <c r="F5" s="8" t="n">
-        <v>24.61</v>
+        <v>317.53</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>24.61</v>
+        <v>317.53</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Alyssa Garcia</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>79.68000000000001</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>79.68000000000001</v>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Alyssa Rodriguez</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>HOST</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Alyssa Rodriguez</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>169.99</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>169.99</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Arnold Ramirez</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Arnold Ramirez</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>General Manager</t>
-        </is>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Arturo Orozco</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>23.43</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Arturo Orozco</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>16.97</v>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Bailee Pena</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>280.36</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>280.36</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Bailee Pena</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>251.18</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>251.18</v>
-      </c>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Blaine Roberson</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>MANAGER</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -778,106 +773,111 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>14.87</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>4.84</v>
-      </c>
+        <v>20.68</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr"/>
       <c r="E11" s="9" t="inlineStr"/>
       <c r="F11" s="8" t="n">
-        <v>419.9</v>
+        <v>327.89</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>419.9</v>
+        <v>327.89</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Blaine Roberson</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>MANAGER</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr"/>
-      <c r="D12" s="9" t="inlineStr"/>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr"/>
-      <c r="G12" s="9" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Bryan Garcia</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>262.67</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>262.67</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Brycen Driver</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>267.22</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>267.22</v>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>308.14</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>308.14</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Clarissa Cantu</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>27.11</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>240.18</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>240.18</v>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>40.00000000000001</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>465.87</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>465.87</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>David Barraza</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>BAR</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>43</v>
+      <c r="C15" s="5" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Dominique Zamora</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>MANAGER</t>
         </is>
@@ -891,19 +891,19 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>BAR</t>
+          <t>SERVER</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>13.51</v>
+        <v>5.43</v>
       </c>
       <c r="D17" s="9" t="inlineStr"/>
       <c r="E17" s="9" t="inlineStr"/>
       <c r="F17" s="8" t="n">
-        <v>263.6</v>
+        <v>21.15</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>263.6</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="18">
@@ -914,161 +914,168 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>SERVER</t>
+          <t>BAR</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>13.93</v>
+        <v>6.48</v>
       </c>
       <c r="D18" s="9" t="inlineStr"/>
       <c r="E18" s="9" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>143.8</v>
+        <v>213.9</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>143.8</v>
+        <v>213.9</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Emileigh Salinas</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>BAR</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
-        <v>26.17</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>477.2</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>477.2</v>
+      <c r="C19" s="5" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>453.35</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>453.35</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Felicity Alaniz</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>146.58</v>
-      </c>
-      <c r="G20" s="11" t="n">
-        <v>166.58</v>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Fernando Acevedo</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Felicity Alaniz</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Gianna Cantu</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Hailey Nunn</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>87.13</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>87.13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Heilyn Julissa Diaz</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
-        <v>31.91</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Gianna Cantu</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>109.23</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>109.23</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Hailey Nunn</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>17.66</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr"/>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="8" t="n">
-        <v>247.38</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>247.38</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Hailey Nunn</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>HOST</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="8" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>15.39</v>
+      <c r="C24" s="5" t="n">
+        <v>34.62</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Heilyn Julissa Diaz</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>34.45999999999999</v>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Indira Garcia</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="8" t="n">
+        <v>318.67</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>318.67</v>
       </c>
     </row>
     <row r="26">
@@ -1083,21 +1090,21 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>10.01</v>
+        <v>23.23</v>
       </c>
       <c r="D26" s="9" t="inlineStr"/>
       <c r="E26" s="9" t="inlineStr"/>
       <c r="F26" s="8" t="n">
-        <v>124</v>
+        <v>336.36</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>124</v>
+        <v>336.36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Indira Garcia</t>
+          <t>Isabel Garcia</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1106,339 +1113,325 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>13.42</v>
+        <v>31.87</v>
       </c>
       <c r="D27" s="9" t="inlineStr"/>
       <c r="E27" s="9" t="inlineStr"/>
       <c r="F27" s="8" t="n">
-        <v>286.47</v>
+        <v>224.14</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>286.47</v>
+        <v>224.14</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Isabel Garcia</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Customer Service Liaison</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>9.289999999999999</v>
+      <c r="C28" s="8" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Isabella Salinas</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="D29" s="9" t="inlineStr"/>
-      <c r="E29" s="9" t="inlineStr"/>
-      <c r="F29" s="8" t="n">
-        <v>499.47</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>499.47</v>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>J'Elle Longoria</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>365.89</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>365.89</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Isabella Salinas</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>18.04</v>
-      </c>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="8" t="n">
-        <v>299.55</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>299.55</v>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ja' Vioun Boyd</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>36.21</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Ja' Vioun Boyd</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Jacari Howard</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n">
-        <v>34.28</v>
+      <c r="C31" s="5" t="n">
+        <v>16.77</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>James Yeomans</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n">
-        <v>39.36</v>
+      <c r="C32" s="5" t="n">
+        <v>36.34</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Jaykob Elizondo</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n">
-        <v>14.38</v>
+      <c r="C33" s="5" t="n">
+        <v>35.88</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Jeremiah Wilhelms</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>28.65</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>341.45</v>
-      </c>
-      <c r="G34" s="11" t="n">
-        <v>341.45</v>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>106.5</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Jessica Bain</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n">
-        <v>26.99</v>
+      <c r="C35" s="5" t="n">
+        <v>30.6</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Joe Palacios</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Jesus Garza</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>23.79</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Jose Cruz</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Kitchen Manager</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>21.31</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Juleus Jones</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>HOST</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>12.93</v>
-      </c>
-      <c r="G36" s="11" t="n">
-        <v>12.93</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Jose Cruz</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Kitchen Manager</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>15.06</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="C38" s="5" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Kaitlyn Esfahani</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>32.34</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>176.33</v>
-      </c>
-      <c r="G38" s="11" t="n">
-        <v>176.33</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>248.59</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>248.59</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Kassidy Pena</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>20.02</v>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>228.37</v>
-      </c>
-      <c r="G39" s="11" t="n">
-        <v>228.37</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>385.13</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>385.13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Kiara Mccoy</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="G40" s="11" t="n">
-        <v>126.3</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Lainey Pickard</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>256.93</v>
-      </c>
-      <c r="G41" s="11" t="n">
-        <v>256.93</v>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>145.1</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Lariah Saenz</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>22.68</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>206.44</v>
-      </c>
-      <c r="G42" s="11" t="n">
-        <v>206.44</v>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>336.41</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>336.41</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Lesli Rodriguez</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Media Admin</t>
         </is>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="C43" s="5" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Maricela Alvarez</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="C44" s="6" t="n">
-        <v>33.18</v>
+      <c r="C44" s="5" t="n">
+        <v>33.67</v>
       </c>
     </row>
     <row r="45">
@@ -1453,15 +1446,15 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>17.11</v>
+        <v>4.41</v>
       </c>
       <c r="D45" s="9" t="inlineStr"/>
       <c r="E45" s="9" t="inlineStr"/>
       <c r="F45" s="8" t="n">
-        <v>176</v>
+        <v>45</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>176</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46">
@@ -1476,258 +1469,187 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>6.42</v>
+        <v>19.99</v>
       </c>
       <c r="D46" s="9" t="inlineStr"/>
       <c r="E46" s="9" t="inlineStr"/>
       <c r="F46" s="8" t="n">
-        <v>113.26</v>
+        <v>225.62</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>113.26</v>
+        <v>225.62</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>MezMarie Sandoval</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>HOST</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G47" s="11" t="n">
-        <v>17</v>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Nicholas Moya</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>32.71</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>Michaela Mireles</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Pablo Ochoa</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>102.49</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>102.49</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Selena Gomez</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Bar Manager</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>393.72</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>393.72</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Sergio Benavente</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Busser</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>26.21</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Sonya Mendez</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>38.21</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Taylor McCarthy</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>87.61</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Victor Moreno</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Director of Catering</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Victoria Cavazos</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>BAR</t>
         </is>
       </c>
-      <c r="C48" s="8" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="D48" s="9" t="inlineStr"/>
-      <c r="E48" s="9" t="inlineStr"/>
-      <c r="F48" s="8" t="n">
-        <v>224.34</v>
-      </c>
-      <c r="G48" s="10" t="n">
-        <v>224.34</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>Michaela Mireles</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="n">
-        <v>14.26</v>
-      </c>
-      <c r="D49" s="9" t="inlineStr"/>
-      <c r="E49" s="9" t="inlineStr"/>
-      <c r="F49" s="8" t="n">
-        <v>95.93000000000001</v>
-      </c>
-      <c r="G49" s="10" t="n">
-        <v>95.93000000000001</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Nicholas Moya</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="n">
-        <v>27.04</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Pablo Ochoa</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>270.66</v>
-      </c>
-      <c r="G51" s="11" t="n">
-        <v>270.66</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Plaxico Vasquez</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="n">
-        <v>16.42</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Selena Gomez</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Bar Manager</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>34.19</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>262.77</v>
-      </c>
-      <c r="G53" s="11" t="n">
-        <v>262.77</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Sonya Mendez</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="n">
-        <v>29.96</v>
+      <c r="C54" s="5" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>67.39</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>67.39</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Victor Moreno</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Director of Catering</t>
-        </is>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>1136.19</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>1101.73</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>34.45999999999999</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>6527.08</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>6532.08</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>Victoria Cavazos</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="D56" s="9" t="inlineStr"/>
-      <c r="E56" s="9" t="inlineStr"/>
-      <c r="F56" s="8" t="n">
-        <v>208.61</v>
-      </c>
-      <c r="G56" s="10" t="n">
-        <v>208.61</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Victoria Cavazos</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="n">
-        <v>18.79</v>
-      </c>
-      <c r="D57" s="9" t="inlineStr"/>
-      <c r="E57" s="9" t="inlineStr"/>
-      <c r="F57" s="8" t="n">
-        <v>201.22</v>
-      </c>
-      <c r="G57" s="10" t="n">
-        <v>201.22</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="n">
-        <v>1113.18</v>
-      </c>
-      <c r="C58" s="6" t="n">
-        <v>1075.24</v>
-      </c>
-      <c r="D58" s="6" t="n">
-        <v>37.94</v>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>7158.5</v>
-      </c>
-      <c r="G58" s="11" t="n">
-        <v>7178.5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Total hours for the BHB Kingsville for the week is 1113.18 of which 37.94 or 3.41% is considered overtime.</t>
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>Total hours for the BHB Kingsville for the week is 1136.19 of which 34.46 or 3.03% is considered overtime.</t>
         </is>
       </c>
     </row>

--- a/Restaurant Management/results/BHB_Kingsville_sorted_Kingsville_Payroll.xlsx
+++ b/Restaurant Management/results/BHB_Kingsville_sorted_Kingsville_Payroll.xlsx
@@ -495,10 +495,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.74</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="3">
@@ -509,19 +506,19 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SERVER</t>
+          <t>BAR</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4.61</v>
+        <v>13.18</v>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>13</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>13</v>
+        <v>87.76000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -532,44 +529,40 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BAR</t>
+          <t>SERVER</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5.4</v>
+        <v>10.13</v>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>65</v>
+        <v>126.39</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>65</v>
+        <v>126.39</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Alyssa Rodriguez</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>HOST</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>20.11</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Alexandra Perez</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="F5" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>91.34999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -584,125 +577,122 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>31.44</v>
+        <v>25.47</v>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>237.84</v>
+        <v>173.08</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>237.84</v>
+        <v>173.08</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Arnold Ramirez</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>General Manager</t>
-        </is>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Alyssa Rodriguez</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>HOST</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Arturo Orozco</t>
+          <t>Arnold Ramirez</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>21.83</v>
+          <t>General Manager</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Austin Barnes</t>
+          <t>Arturo Orozco</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>SERVER</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="F9" t="n">
-        <v>252.59</v>
-      </c>
-      <c r="G9" t="n">
-        <v>252.59</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>Austin Barnes</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="F10" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39.18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>Bailee Pena</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>33.71</v>
-      </c>
-      <c r="F10" t="n">
-        <v>229.35</v>
-      </c>
-      <c r="G10" t="n">
-        <v>229.35</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="F11" t="n">
+        <v>253.05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>253.05</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Blaine Roberson</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="n">
-        <v>290.5</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>290.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Blaine Roberson</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>MANAGER</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -716,13 +706,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.949999999999999</v>
+        <v>6.09</v>
       </c>
       <c r="F13" t="n">
-        <v>109.5</v>
+        <v>153.97</v>
       </c>
       <c r="G13" t="n">
-        <v>109.5</v>
+        <v>153.97</v>
       </c>
     </row>
     <row r="14">
@@ -737,73 +727,73 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12.74</v>
+        <v>34.08</v>
       </c>
       <c r="F14" t="n">
-        <v>174.43</v>
+        <v>322.62</v>
       </c>
       <c r="G14" t="n">
-        <v>174.43</v>
+        <v>322.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Clarissa Cantu</t>
+          <t>Cameron Allen</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>SERVER</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36.41</v>
-      </c>
-      <c r="F15" t="n">
-        <v>322.16</v>
-      </c>
-      <c r="G15" t="n">
-        <v>322.16</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Dominique Zamora</t>
+          <t>Christopher Campos</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>MANAGER</t>
-        </is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>36.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Emileigh Salinas</t>
+          <t>Clarissa Cantu</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>BAR</t>
+          <t>SERVER</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.56</v>
+        <v>40</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.51</v>
       </c>
       <c r="F17" t="n">
-        <v>342.7</v>
+        <v>325.43</v>
       </c>
       <c r="G17" t="n">
-        <v>342.7</v>
+        <v>325.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Felicity Alaniz</t>
+          <t>David Barraza</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
@@ -812,19 +802,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.92</v>
-      </c>
-      <c r="F18" t="n">
-        <v>150.03</v>
-      </c>
-      <c r="G18" t="n">
-        <v>150.03</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Gina Galvan</t>
+          <t>David Hernandez</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
@@ -833,49 +817,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.56</v>
+        <v>23.98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Hailey Nunn</t>
+          <t>Dominique Zamora</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>20.93</v>
-      </c>
-      <c r="F20" t="n">
-        <v>223.83</v>
-      </c>
-      <c r="G20" t="n">
-        <v>223.83</v>
+          <t>MANAGER</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Heilyn Julissa Diaz</t>
+          <t>Elizabeth Williams</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>HOST</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>36.49</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Indira Garcia</t>
+          <t>Emileigh Salinas</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
@@ -884,161 +859,160 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.14</v>
+        <v>29.07</v>
       </c>
       <c r="F22" t="n">
-        <v>215.2</v>
+        <v>263.12</v>
       </c>
       <c r="G22" t="n">
-        <v>215.2</v>
+        <v>263.12</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Isabel Garcia</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>17.09</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="n">
-        <v>212.28</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>212.28</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Felicity Alaniz</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="G23" t="n">
+        <v>61.84</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Isabel Garcia</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Customer Service Liaison</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Gilbert Garza</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>38.36</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Isabella Salinas</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="n">
-        <v>62.76</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>62.76</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Hailey Nunn</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="F25" t="n">
+        <v>240.09</v>
+      </c>
+      <c r="G25" t="n">
+        <v>240.09</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Isabella Salinas</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="n">
-        <v>281.41</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>281.41</v>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Heilyn Julissa Diaz</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>40</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>J'Elle Longoria</t>
+          <t>Indira Garcia</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>SERVER</t>
+          <t>BAR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>29.66</v>
+        <v>27.39</v>
       </c>
       <c r="F27" t="n">
-        <v>224.41</v>
+        <v>339.91</v>
       </c>
       <c r="G27" t="n">
-        <v>224.41</v>
+        <v>339.91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Ja' Vioun Boyd</t>
+          <t>Isabel Garcia</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>SERVER</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>40</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.33</v>
+        <v>22.72</v>
+      </c>
+      <c r="F28" t="n">
+        <v>162.43</v>
+      </c>
+      <c r="G28" t="n">
+        <v>162.43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Jacari Howard</t>
+          <t>J'Elle Longoria</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>SERVER</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>21.83</v>
+        <v>26.11</v>
+      </c>
+      <c r="F29" t="n">
+        <v>79.44</v>
+      </c>
+      <c r="G29" t="n">
+        <v>79.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>James Yeomans</t>
+          <t>Ja' Vioun Boyd</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
@@ -1047,74 +1021,64 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>39.24</v>
+        <v>39.99999999999999</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.62</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
+          <t>Jacari Howard</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>30.26</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>James Yeomans</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>38.23</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
           <t>Jaykob Elizondo</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>35.29</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Jeremiah Wilhelms</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="n">
-        <v>139.65</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>139.65</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Jeremiah Wilhelms</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="n">
-        <v>35.38</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>35.38</v>
+      <c r="C33" t="n">
+        <v>40</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Jessica Bain</t>
+          <t>Jesus Garza</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
@@ -1123,7 +1087,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>30.05</v>
+        <v>30.82</v>
       </c>
     </row>
     <row r="35">
@@ -1156,13 +1120,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14.23</v>
+        <v>13.02</v>
       </c>
       <c r="F36" t="n">
-        <v>103.9</v>
+        <v>88</v>
       </c>
       <c r="G36" t="n">
-        <v>103.9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37">
@@ -1177,13 +1141,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>26.14</v>
+        <v>18.89</v>
       </c>
       <c r="F37" t="n">
-        <v>374.58</v>
+        <v>109.26</v>
       </c>
       <c r="G37" t="n">
-        <v>374.58</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="38">
@@ -1198,13 +1162,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>28.63</v>
+        <v>26.11</v>
       </c>
       <c r="F38" t="n">
-        <v>269.74</v>
+        <v>236.71</v>
       </c>
       <c r="G38" t="n">
-        <v>269.74</v>
+        <v>236.71</v>
       </c>
     </row>
     <row r="39">
@@ -1219,55 +1183,59 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>14.57</v>
+        <v>12.83</v>
       </c>
       <c r="F39" t="n">
-        <v>213.96</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>213.96</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Kiara Mccoy</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="F40" t="n">
-        <v>13</v>
-      </c>
-      <c r="G40" t="n">
-        <v>13</v>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>21.14</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>Lariah Saenz</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="F41" t="n">
-        <v>299.03</v>
-      </c>
-      <c r="G41" t="n">
-        <v>299.03</v>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Kiara Mccoy</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="n">
+        <v>148.54</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>148.54</v>
       </c>
     </row>
     <row r="42">
@@ -1297,13 +1265,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>18.74</v>
+        <v>23.27</v>
       </c>
       <c r="F43" t="n">
-        <v>124.13</v>
+        <v>191.17</v>
       </c>
       <c r="G43" t="n">
-        <v>124.13</v>
+        <v>191.17</v>
       </c>
     </row>
     <row r="44">
@@ -1325,52 +1293,53 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>34.53</v>
+        <v>8.559999999999999</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Michaela Mireles</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>BAR</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>20.09</v>
-      </c>
-      <c r="F46" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="G46" t="n">
-        <v>166.8</v>
+      <c r="C46" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="n">
+        <v>254.55</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>254.55</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>Noel Rodriguez</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>HOST</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>9</v>
-      </c>
-      <c r="E47" t="n">
-        <v>7</v>
-      </c>
-      <c r="F47" t="n">
-        <v>9</v>
-      </c>
-      <c r="G47" t="n">
-        <v>16</v>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Michaela Mireles</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -1385,85 +1354,101 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11.98</v>
+        <v>12.92</v>
       </c>
       <c r="F48" t="n">
-        <v>115.37</v>
+        <v>34.74</v>
       </c>
       <c r="G48" t="n">
-        <v>115.37</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Selena Gomez</t>
+          <t>Selena Cuellar</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Bar Manager</t>
+          <t>SERVER</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>33.31</v>
+        <v>30.68</v>
       </c>
       <c r="F49" t="n">
-        <v>239.9</v>
+        <v>266.31</v>
       </c>
       <c r="G49" t="n">
-        <v>239.9</v>
+        <v>266.31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Sergio Benavente</t>
+          <t>Selena Gomez</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Busser</t>
+          <t>Bar Manager</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>18.4</v>
+        <v>32.31</v>
+      </c>
+      <c r="F50" t="n">
+        <v>168.61</v>
+      </c>
+      <c r="G50" t="n">
+        <v>168.61</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>Sonya Mendez</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>26.23</v>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Taylor McCarthy</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SERVER</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Taylor McCarthy</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>SERVER</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="F52" t="n">
-        <v>188.58</v>
-      </c>
-      <c r="G52" t="n">
-        <v>188.58</v>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="n">
+        <v>114.41</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>114.41</v>
       </c>
     </row>
     <row r="53">
@@ -1485,28 +1470,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1045.65</v>
+        <v>1089.54</v>
       </c>
       <c r="C54" t="n">
-        <v>1018.59</v>
+        <v>1048.39</v>
       </c>
       <c r="D54" t="n">
-        <v>27.06000000000001</v>
+        <v>41.15000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F54" t="n">
-        <v>5720.120000000001</v>
+        <v>4592</v>
       </c>
       <c r="G54" t="n">
-        <v>5727.120000000001</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Total hours for the BHB Kingsville for the week is 1045.65 of which 27.06 or 2.59% is considered overtime.</t>
+          <t>Total hours for the BHB Kingsville for the week is 1089.54 of which 41.15 or 3.78% is considered overtime.</t>
         </is>
       </c>
     </row>
